--- a/sales.xlsx
+++ b/sales.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dataPython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C30E8B6-52FB-4EF1-8262-55A0E5816D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A6FFCA-786B-44E2-AB09-C46A62ABA75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-11000" windowWidth="38620" windowHeight="21100" xr2:uid="{6A4E7066-5E12-46EB-97A4-E0E6E0A19172}"/>
+    <workbookView xWindow="25480" yWindow="-7520" windowWidth="17280" windowHeight="9740" xr2:uid="{6A4E7066-5E12-46EB-97A4-E0E6E0A19172}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="매출" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
